--- a/public/raw-entry-data/b2c/iOS.xlsx
+++ b/public/raw-entry-data/b2c/iOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alfa/web-alfa/tr-b2c/tech-radar/public/raw-entry-data/b2c/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CD81A9-6428-7547-A2BB-3FA1F7EA153D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A6DFFF-845C-1346-BC2E-523B7C56FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="7700" windowWidth="31840" windowHeight="12300" xr2:uid="{D0E5AF86-51E4-4329-BFCB-5FE4200F8556}"/>
+    <workbookView xWindow="2720" yWindow="7700" windowWidth="31840" windowHeight="12300" xr2:uid="{D0E5AF86-51E4-4329-BFCB-5FE4200F8556}"/>
   </bookViews>
   <sheets>
     <sheet name="radar" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="68">
   <si>
     <t>Ноль</t>
   </si>
@@ -232,6 +232,18 @@
   </si>
   <si>
     <t>UIKit — фреймворк для разработки пользовательского интерфейса в приложениях для iOS</t>
+  </si>
+  <si>
+    <t>metrics</t>
+  </si>
+  <si>
+    <t>https://yandex.ru/support/appmetrica-io/ru/</t>
+  </si>
+  <si>
+    <t>Yandex Appmetrica</t>
+  </si>
+  <si>
+    <t>это платформа полного цикла для аналитики и роста мобильного приложения</t>
   </si>
 </sst>
 </file>
@@ -695,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E083F0B-9B6B-4AE1-B88F-228D13850335}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -876,6 +888,26 @@
       </c>
       <c r="G8" s="4" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -900,25 +932,25 @@
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>F9:F37</xm:sqref>
+          <xm:sqref>F10:F37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6857320C-10DD-4851-98FA-A3CA686293DC}">
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>E9:E34</xm:sqref>
+          <xm:sqref>E10:E34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5AFEE91B-7A0C-0045-8A32-2A47382063B4}">
           <x14:formula1>
             <xm:f>rings!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F3:F8</xm:sqref>
+          <xm:sqref>F3:F9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E5D21C0-46D9-574F-924F-47FF86B1D17A}">
           <x14:formula1>
             <xm:f>quadrants!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E8</xm:sqref>
+          <xm:sqref>E3:E9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ECCB302B-B329-497F-B6B4-042AE8F9E14B}">
           <x14:formula1>
